--- a/file/SeeingAI_iOS_Android_VPATJ13462.xlsx
+++ b/file/SeeingAI_iOS_Android_VPATJ13462.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C281697-37FF-4037-92FB-6F22E0545F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFFC3266-B773-4A36-9F6D-B7A82320078B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{933B6064-5ADF-4889-AC91-73E5528546F2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{AC846A67-6B2F-4E46-B99F-11E99A8C5B12}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
     <t>ICT機器・サービスのアクセシビリティ自己評価様式</t>
   </si>
   <si>
-    <t>作成日：2026年9月24日</t>
+    <t>作成日：2025年9月22日</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1933,8 +1933,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4036130B-29DF-4D17-AEC7-C910259CF898}">
-  <sheetPr codeName="Sheet321">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E8B74C6-CDBB-4337-8411-11609CB23E19}">
+  <sheetPr codeName="Sheet353">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -2749,7 +2749,7 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{4095DA73-6C58-4B4E-A800-ACBC8BB58B57}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{C6973197-DCB8-4C09-8E1A-F6B9CED45B55}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -2757,7 +2757,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{378AAC96-FA32-4E83-8507-9F978B010161}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA162170-D100-4029-B75A-214ABAABF98A}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
